--- a/data/trans_orig/P19C11_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P19C11_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por implantes / solo 2023 en 2023</t>
+          <t>Población según si el motivo por su última visita al dentista fue por implantes / solo 2023 en 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21909</t>
+          <t>21265</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42818</t>
+          <t>42032</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16896</t>
+          <t>16170</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32214</t>
+          <t>31737</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41914</t>
+          <t>41108</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66920</t>
+          <t>67983</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>455664</t>
+          <t>456450</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>476573</t>
+          <t>477217</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>408711</t>
+          <t>409188</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>424029</t>
+          <t>424755</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>872487</t>
+          <t>871424</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>897493</t>
+          <t>898299</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,62%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14684</t>
+          <t>14487</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31391</t>
+          <t>30905</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8354</t>
+          <t>8094</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20602</t>
+          <t>19796</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25468</t>
+          <t>26067</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45768</t>
+          <t>46895</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>417027</t>
+          <t>417513</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>433734</t>
+          <t>433931</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>357004</t>
+          <t>357810</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>369252</t>
+          <t>369512</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>780255</t>
+          <t>779128</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>800555</t>
+          <t>799956</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,84%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5530</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32108</t>
+          <t>31651</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7029</t>
+          <t>6961</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16670</t>
+          <t>17286</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12645</t>
+          <t>10173</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45657</t>
+          <t>44606</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>628621</t>
+          <t>629078</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>655199</t>
+          <t>655523</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>148298</t>
+          <t>147682</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>157939</t>
+          <t>158007</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>780040</t>
+          <t>781091</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>813052</t>
+          <t>815524</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43262</t>
+          <t>42992</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>73242</t>
+          <t>72491</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14393</t>
+          <t>14609</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41426</t>
+          <t>41864</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>60564</t>
+          <t>61834</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>106858</t>
+          <t>108565</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>924909</t>
+          <t>925660</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>954889</t>
+          <t>955159</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>917443</t>
+          <t>917005</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>944476</t>
+          <t>944260</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1850162</t>
+          <t>1848455</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1896456</t>
+          <t>1895186</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,84%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>5120</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18617</t>
+          <t>18086</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22960</t>
+          <t>22678</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43392</t>
+          <t>44503</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31027</t>
+          <t>31934</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53283</t>
+          <t>54754</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>420235</t>
+          <t>420766</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>433862</t>
+          <t>433732</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>770589</t>
+          <t>769478</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>791021</t>
+          <t>791303</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1199550</t>
+          <t>1198079</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1221806</t>
+          <t>1220899</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,45%</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2486</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17050</t>
+          <t>17012</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34058</t>
+          <t>34166</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17708</t>
+          <t>18150</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35003</t>
+          <t>35160</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>230204</t>
+          <t>230726</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>709852</t>
+          <t>709744</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>726860</t>
+          <t>726898</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>942119</t>
+          <t>941962</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>959414</t>
+          <t>958972</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>105172</t>
+          <t>107076</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>163504</t>
+          <t>164267</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>107703</t>
+          <t>105594</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>155973</t>
+          <t>154244</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>228873</t>
+          <t>230725</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>306490</t>
+          <t>307701</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3114339</t>
+          <t>3113576</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3172671</t>
+          <t>3170767</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3344286</t>
+          <t>3346015</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3392556</t>
+          <t>3394665</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6471612</t>
+          <t>6470401</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6549229</t>
+          <t>6547377</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,6%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19C11_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P19C11_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>30547</t>
+          <t>32454</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21265</t>
+          <t>22910</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42032</t>
+          <t>44194</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>23256</t>
+          <t>24401</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16170</t>
+          <t>16930</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31737</t>
+          <t>34053</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>53803</t>
+          <t>56855</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41108</t>
+          <t>44966</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67983</t>
+          <t>71205</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>467935</t>
+          <t>508809</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>456450</t>
+          <t>497069</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>477217</t>
+          <t>518353</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>417669</t>
+          <t>456926</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>409188</t>
+          <t>447274</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>424755</t>
+          <t>464397</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>885604</t>
+          <t>965735</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>871424</t>
+          <t>951385</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>898299</t>
+          <t>977624</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>498482</t>
+          <t>541263</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>498482</t>
+          <t>541263</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>498482</t>
+          <t>541263</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>440925</t>
+          <t>481327</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>440925</t>
+          <t>481327</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>440925</t>
+          <t>481327</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>939407</t>
+          <t>1022590</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>939407</t>
+          <t>1022590</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>939407</t>
+          <t>1022590</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21416</t>
+          <t>22737</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14487</t>
+          <t>15510</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30905</t>
+          <t>32649</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13239</t>
+          <t>13926</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8094</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19796</t>
+          <t>21312</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>34655</t>
+          <t>36663</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26067</t>
+          <t>26949</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46895</t>
+          <t>48030</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>427002</t>
+          <t>456595</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>417513</t>
+          <t>446683</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>433931</t>
+          <t>463822</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>364367</t>
+          <t>403994</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>357810</t>
+          <t>396608</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>369512</t>
+          <t>409051</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>791368</t>
+          <t>860590</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>779128</t>
+          <t>849223</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>799956</t>
+          <t>870304</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>97,0%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>448418</t>
+          <t>479332</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>448418</t>
+          <t>479332</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>448418</t>
+          <t>479332</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>377606</t>
+          <t>417920</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>377606</t>
+          <t>417920</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>377606</t>
+          <t>417920</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>826023</t>
+          <t>897253</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>826023</t>
+          <t>897253</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>826023</t>
+          <t>897253</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>17233</t>
+          <t>18416</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5206</t>
+          <t>11659</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31651</t>
+          <t>27857</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11066</t>
+          <t>11667</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6961</t>
+          <t>7543</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17286</t>
+          <t>17359</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>28298</t>
+          <t>30084</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10173</t>
+          <t>22155</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44606</t>
+          <t>41990</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>643496</t>
+          <t>445449</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>629078</t>
+          <t>436008</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>655523</t>
+          <t>452206</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>153902</t>
+          <t>173166</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>147682</t>
+          <t>167474</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>158007</t>
+          <t>177290</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>797399</t>
+          <t>618614</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>781091</t>
+          <t>606708</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>815524</t>
+          <t>626543</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>96,58%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>660729</t>
+          <t>463865</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>660729</t>
+          <t>463865</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>660729</t>
+          <t>463865</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>164968</t>
+          <t>184833</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>164968</t>
+          <t>184833</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>164968</t>
+          <t>184833</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>825697</t>
+          <t>648698</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>825697</t>
+          <t>648698</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>825697</t>
+          <t>648698</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>57735</t>
+          <t>63208</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42992</t>
+          <t>47626</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>72491</t>
+          <t>79142</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>29575</t>
+          <t>34040</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14609</t>
+          <t>25371</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41864</t>
+          <t>42957</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>87311</t>
+          <t>97248</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61834</t>
+          <t>79644</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>108565</t>
+          <t>118552</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>940416</t>
+          <t>1032491</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>925660</t>
+          <t>1016557</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>955159</t>
+          <t>1048073</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>929294</t>
+          <t>802750</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>917005</t>
+          <t>793833</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>944260</t>
+          <t>811419</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1869709</t>
+          <t>1835241</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1848455</t>
+          <t>1813937</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1895186</t>
+          <t>1852845</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>95,88%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>998151</t>
+          <t>1095699</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>998151</t>
+          <t>1095699</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>998151</t>
+          <t>1095699</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>958869</t>
+          <t>836790</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>958869</t>
+          <t>836790</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>958869</t>
+          <t>836790</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1957020</t>
+          <t>1932489</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1957020</t>
+          <t>1932489</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1957020</t>
+          <t>1932489</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>9698</t>
+          <t>14200</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5120</t>
+          <t>8189</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18086</t>
+          <t>23510</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>32188</t>
+          <t>34967</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22678</t>
+          <t>26963</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44503</t>
+          <t>45317</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>41885</t>
+          <t>49167</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31934</t>
+          <t>39847</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54754</t>
+          <t>62905</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>429154</t>
+          <t>495648</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>420766</t>
+          <t>486338</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>433732</t>
+          <t>501659</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>781793</t>
+          <t>758538</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>769478</t>
+          <t>748188</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>791303</t>
+          <t>766542</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1210948</t>
+          <t>1254186</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1198079</t>
+          <t>1240448</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1220899</t>
+          <t>1263506</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>96,94%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>438852</t>
+          <t>509848</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>438852</t>
+          <t>509848</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>438852</t>
+          <t>509848</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>813981</t>
+          <t>793505</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>813981</t>
+          <t>793505</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>813981</t>
+          <t>793505</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1252833</t>
+          <t>1303353</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1252833</t>
+          <t>1303353</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1252833</t>
+          <t>1303353</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>507</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2486</t>
+          <t>2590</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>24172</t>
+          <t>25564</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17012</t>
+          <t>17955</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34166</t>
+          <t>34928</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>24693</t>
+          <t>26071</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18150</t>
+          <t>18060</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35160</t>
+          <t>37011</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -2553,17 +2553,17 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>232691</t>
+          <t>225280</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>230726</t>
+          <t>223197</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>233212</t>
+          <t>225787</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>719738</t>
+          <t>793178</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>709744</t>
+          <t>783814</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>726898</t>
+          <t>800787</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>952429</t>
+          <t>1018458</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>941962</t>
+          <t>1007518</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>958972</t>
+          <t>1026469</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>233212</t>
+          <t>225787</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>233212</t>
+          <t>225787</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>233212</t>
+          <t>225787</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>743910</t>
+          <t>818742</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>743910</t>
+          <t>818742</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>743910</t>
+          <t>818742</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>977122</t>
+          <t>1044529</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>977122</t>
+          <t>1044529</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>977122</t>
+          <t>1044529</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>137150</t>
+          <t>151523</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>107076</t>
+          <t>131892</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>164267</t>
+          <t>178506</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>133495</t>
+          <t>144564</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>105594</t>
+          <t>129687</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>154244</t>
+          <t>166928</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>270645</t>
+          <t>296087</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>230725</t>
+          <t>269459</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>307701</t>
+          <t>330897</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3140693</t>
+          <t>3164272</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3113576</t>
+          <t>3137289</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3170767</t>
+          <t>3183903</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3366764</t>
+          <t>3388554</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3346015</t>
+          <t>3366190</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3394665</t>
+          <t>3403431</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6507457</t>
+          <t>6552826</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6470401</t>
+          <t>6518016</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6547377</t>
+          <t>6579454</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3277843</t>
+          <t>3315795</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3277843</t>
+          <t>3315795</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3277843</t>
+          <t>3315795</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3500259</t>
+          <t>3533118</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3500259</t>
+          <t>3533118</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3500259</t>
+          <t>3533118</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6778102</t>
+          <t>6848913</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6778102</t>
+          <t>6848913</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6778102</t>
+          <t>6848913</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
